--- a/data/trans_dic/P1806_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,29; 3,04</t>
+          <t>0,24; 2,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,58</t>
+          <t>0,21; 1,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,84</t>
+          <t>0,37; 1,89</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,35</t>
+          <t>0,7; 3,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,5; 6,6</t>
+          <t>3,34; 6,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,39</t>
+          <t>2,42; 4,45</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,73</t>
+          <t>1,97; 5,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,24; 12,06</t>
+          <t>7,29; 12,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,48</t>
+          <t>5,13; 8,31</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,23</t>
+          <t>1,68; 6,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,45</t>
+          <t>2,55; 6,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,71; 5,6</t>
+          <t>2,74; 5,47</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,36</t>
+          <t>0,93; 4,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,51</t>
+          <t>2,29; 5,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,23</t>
+          <t>1,93; 4,24</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,6; 6,94</t>
+          <t>1,77; 7,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,87; 8,77</t>
+          <t>3,74; 8,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,14; 6,32</t>
+          <t>3,05; 6,29</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 6,86</t>
+          <t>2,79; 6,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,39; 10,17</t>
+          <t>3,55; 10,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,87; 7,64</t>
+          <t>3,84; 7,76</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,39</t>
+          <t>0,19; 1,34</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,05</t>
+          <t>1,43; 3,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,66; 1,79</t>
+          <t>0,73; 1,87</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,74; 2,96</t>
+          <t>1,7; 2,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 5,62</t>
+          <t>3,95; 5,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,16</t>
+          <t>3,14; 4,12</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>888; 9475</t>
+          <t>761; 9103</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>663; 4579</t>
+          <t>616; 4246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2156; 11073</t>
+          <t>2227; 11351</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4038; 17366</t>
+          <t>3606; 18137</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17982; 33906</t>
+          <t>17144; 34558</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>23045; 45351</t>
+          <t>25024; 45946</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6566; 18114</t>
+          <t>6232; 18104</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25282; 42098</t>
+          <t>25447; 42065</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34950; 56427</t>
+          <t>34109; 55280</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5602; 19480</t>
+          <t>5258; 19508</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12296; 30694</t>
+          <t>12154; 30972</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21393; 44145</t>
+          <t>21624; 43109</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1638; 7802</t>
+          <t>1670; 7624</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4590; 11501</t>
+          <t>4772; 11220</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7565; 16368</t>
+          <t>7478; 16437</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4318; 18701</t>
+          <t>4770; 19459</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9936; 22550</t>
+          <t>9620; 21238</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16549; 33299</t>
+          <t>16053; 33151</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>18694; 42834</t>
+          <t>17417; 42397</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>28805; 86364</t>
+          <t>30170; 87658</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56990; 112614</t>
+          <t>56549; 114355</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1943; 12890</t>
+          <t>1741; 12485</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9599; 21863</t>
+          <t>10258; 22844</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>10813; 29518</t>
+          <t>11994; 30779</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>60157; 102574</t>
+          <t>58876; 98977</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>145653; 205827</t>
+          <t>144518; 207013</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>223998; 295999</t>
+          <t>223470; 293469</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1806_2023-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P1806_2023-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,92</t>
+          <t>0,32; 2,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,47</t>
+          <t>0,31; 1,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,89</t>
+          <t>0,43; 1,74</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,7; 3,5</t>
+          <t>0,75; 3,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,73</t>
+          <t>3,08; 6,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,42; 4,45</t>
+          <t>2,29; 4,36</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,97; 5,73</t>
+          <t>1,91; 5,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,29; 12,05</t>
+          <t>7,48; 12,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,13; 8,31</t>
+          <t>5,19; 8,2</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,24</t>
+          <t>1,47; 5,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 6,51</t>
+          <t>4,02; 7,33</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,47</t>
+          <t>3,15; 5,71</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,27</t>
+          <t>0,86; 4,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,38</t>
+          <t>2,09; 5,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,24</t>
+          <t>1,87; 4,02</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,77; 7,22</t>
+          <t>1,56; 5,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,74; 8,26</t>
+          <t>3,72; 8,34</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3,05; 6,29</t>
+          <t>2,96; 6,12</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,72%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 6,79</t>
+          <t>2,7; 6,15</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,55; 10,32</t>
+          <t>7,3; 11,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,84; 7,76</t>
+          <t>5,52; 8,24</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,19; 1,34</t>
+          <t>0,38; 1,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 3,18</t>
+          <t>1,27; 2,9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,73; 1,87</t>
+          <t>0,98; 2,01</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,86</t>
+          <t>1,84; 2,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,95; 5,65</t>
+          <t>4,59; 5,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3,14; 4,12</t>
+          <t>3,4; 4,19</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1834</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5957</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>761; 9103</t>
+          <t>1016; 7971</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>616; 4246</t>
+          <t>967; 5434</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2227; 11351</t>
+          <t>2755; 11038</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>8908</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>24485</t>
+          <t>24879</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>33391</t>
+          <t>33787</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3606; 18137</t>
+          <t>3955; 17157</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17144; 34558</t>
+          <t>16781; 34613</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25024; 45946</t>
+          <t>24606; 46923</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10800</t>
+          <t>10604</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>33132</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43932</t>
+          <t>44330</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6232; 18104</t>
+          <t>6036; 17739</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25447; 42065</t>
+          <t>26649; 43471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>34109; 55280</t>
+          <t>34886; 55164</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>9915</t>
+          <t>10171</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>21377</t>
+          <t>23473</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>31292</t>
+          <t>33644</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5258; 19508</t>
+          <t>5488; 21527</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12154; 30972</t>
+          <t>16957; 30930</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21624; 43109</t>
+          <t>25016; 45411</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7421</t>
+          <t>7779</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11416</t>
+          <t>12023</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1670; 7624</t>
+          <t>1769; 8722</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4772; 11220</t>
+          <t>4751; 11973</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>7478; 16437</t>
+          <t>8083; 17392</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>14340</t>
+          <t>14537</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23314</t>
+          <t>22686</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4770; 19459</t>
+          <t>4216; 15746</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>9620; 21238</t>
+          <t>9807; 21985</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16053; 33151</t>
+          <t>15807; 32689</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>27795</t>
+          <t>29745</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>61714</t>
+          <t>70466</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>89509</t>
+          <t>100211</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>17417; 42397</t>
+          <t>19445; 44296</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>30170; 87658</t>
+          <t>56380; 87841</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>56549; 114355</t>
+          <t>82332; 122941</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>5928</t>
+          <t>6598</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>16843</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>21021</t>
+          <t>23441</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1741; 12485</t>
+          <t>3012; 13242</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>10258; 22844</t>
+          <t>10583; 24148</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11994; 30779</t>
+          <t>15917; 32830</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>79627</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>179396</t>
+          <t>194137</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>259023</t>
+          <t>276079</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>58876; 98977</t>
+          <t>65067; 102269</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>144518; 207013</t>
+          <t>171546; 218572</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>223470; 293469</t>
+          <t>246892; 304186</t>
         </is>
       </c>
     </row>
